--- a/artfynd/A 63545-2023 artfynd.xlsx
+++ b/artfynd/A 63545-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 63545-2023 artfynd.xlsx
+++ b/artfynd/A 63545-2023 artfynd.xlsx
@@ -796,11 +796,11 @@
         <v>113682486</v>
       </c>
       <c r="B3" t="n">
-        <v>90774</v>
+        <v>91168</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">

--- a/artfynd/A 63545-2023 artfynd.xlsx
+++ b/artfynd/A 63545-2023 artfynd.xlsx
@@ -796,7 +796,7 @@
         <v>113682486</v>
       </c>
       <c r="B3" t="n">
-        <v>91168</v>
+        <v>91182</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 63545-2023 artfynd.xlsx
+++ b/artfynd/A 63545-2023 artfynd.xlsx
@@ -796,7 +796,7 @@
         <v>113682486</v>
       </c>
       <c r="B3" t="n">
-        <v>91182</v>
+        <v>91184</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 63545-2023 artfynd.xlsx
+++ b/artfynd/A 63545-2023 artfynd.xlsx
@@ -796,7 +796,7 @@
         <v>113682486</v>
       </c>
       <c r="B3" t="n">
-        <v>91184</v>
+        <v>91185</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 63545-2023 artfynd.xlsx
+++ b/artfynd/A 63545-2023 artfynd.xlsx
@@ -796,7 +796,7 @@
         <v>113682486</v>
       </c>
       <c r="B3" t="n">
-        <v>91185</v>
+        <v>91194</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
